--- a/content/post/drafts/weekly-picks/2025Lillehammer/ladies-points.xlsx
+++ b/content/post/drafts/weekly-picks/2025Lillehammer/ladies-points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="386">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -257,6 +257,63 @@
     <t xml:space="preserve">99.8202222268068</t>
   </si>
   <si>
+    <t xml:space="preserve">Delphine Claudel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6809595395137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1467543579797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1809239808619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0086378783553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helene Marie Fossesholm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0584924625355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.774241584081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8327340466165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flora Dolci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3753260494591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.11454052692315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7720796953885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2619462717707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1107754526239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4504906852012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.5612661378251</t>
+  </si>
+  <si>
     <t xml:space="preserve">Katerina Janatova</t>
   </si>
   <si>
@@ -266,70 +323,13 @@
     <t xml:space="preserve">37.6585200550363</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1570496045167</t>
+    <t xml:space="preserve">28.1084268958764</t>
   </si>
   <si>
     <t xml:space="preserve">15.8974675274071</t>
   </si>
   <si>
-    <t xml:space="preserve">98.7130371869601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delphine Claudel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6809595395137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1467543579797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1809239808619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0086378783553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helene Marie Fossesholm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0584924625355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.774241584081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8327340466165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flora Dolci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3753260494591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.11454052692315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7720796953885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2619462717707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1107754526239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4504906852012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.5612661378251</t>
+    <t xml:space="preserve">81.6644144783199</t>
   </si>
   <si>
     <t xml:space="preserve">Sophia Laukli</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">Sonjaa Schmidt</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15134408432258</t>
+    <t xml:space="preserve">5.15629395575086</t>
   </si>
   <si>
     <t xml:space="preserve">16.4191319400782</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">7.87939095653348</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4498669809343</t>
+    <t xml:space="preserve">29.4548168523626</t>
   </si>
   <si>
     <t xml:space="preserve">Izabela Marcisz</t>
@@ -791,27 +791,30 @@
     <t xml:space="preserve">22.281474791961</t>
   </si>
   <si>
+    <t xml:space="preserve">Masae Tsuchiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37983269864639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.227638176348099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1970200542553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8044909292497</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hedda Østberg Amundsen</t>
   </si>
   <si>
     <t xml:space="preserve">21.7630500297892</t>
   </si>
   <si>
-    <t xml:space="preserve">Masae Tsuchiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37983269864639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1970200542553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5768527529016</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anna Comarella</t>
   </si>
   <si>
@@ -836,10 +839,10 @@
     <t xml:space="preserve">4.63925131265287</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7577714886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3970228012905</t>
+    <t xml:space="preserve">15.8485822715946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4878335842474</t>
   </si>
   <si>
     <t xml:space="preserve">Chika Honda</t>
@@ -848,10 +851,13 @@
     <t xml:space="preserve">4.54764758727049</t>
   </si>
   <si>
+    <t xml:space="preserve">0.407244932649063</t>
+  </si>
+  <si>
     <t xml:space="preserve">14.6780776250535</t>
   </si>
   <si>
-    <t xml:space="preserve">19.225725212324</t>
+    <t xml:space="preserve">19.632970144973</t>
   </si>
   <si>
     <t xml:space="preserve">Lisa Lohmann</t>
@@ -911,7 +917,7 @@
     <t xml:space="preserve">10.5672616149283</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7186056992509</t>
+    <t xml:space="preserve">15.7235555706792</t>
   </si>
   <si>
     <t xml:space="preserve">Keidy Kaasiku</t>
@@ -935,7 +941,7 @@
     <t xml:space="preserve">7.50625519014015</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0889450761083</t>
+    <t xml:space="preserve">14.0938949475365</t>
   </si>
   <si>
     <t xml:space="preserve">Amalie Håkonsen Ous</t>
@@ -1019,6 +1025,12 @@
     <t xml:space="preserve">9.9368916632222</t>
   </si>
   <si>
+    <t xml:space="preserve">Berit Mogstad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90305143400125</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anne Kyllönen</t>
   </si>
   <si>
@@ -1058,21 +1070,27 @@
     <t xml:space="preserve">Chika Kobayashi</t>
   </si>
   <si>
+    <t xml:space="preserve">0.375311903368497</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.51838869837888</t>
   </si>
   <si>
+    <t xml:space="preserve">5.89370060174738</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tuva Anine Brusveen-Jensen</t>
   </si>
   <si>
+    <t xml:space="preserve">Kamila YELGAZINOVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mali Eidnes BAKKEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">Katharina BRUDERMANN</t>
   </si>
   <si>
-    <t xml:space="preserve">Mali Eidnes BAKKEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamila YELGAZINOVA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mali Eidnes Bakken</t>
   </si>
   <si>
@@ -1121,9 +1139,15 @@
     <t xml:space="preserve">Barbora Havlickova</t>
   </si>
   <si>
+    <t xml:space="preserve">0.153751524236983</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.31297460968772</t>
   </si>
   <si>
+    <t xml:space="preserve">2.46672613392471</t>
+  </si>
+  <si>
     <t xml:space="preserve">Amanda Saari</t>
   </si>
   <si>
@@ -1137,9 +1161,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ingrid Bergene Aabrekk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.407244932649063</t>
   </si>
   <si>
     <t xml:space="preserve">Kseniya Shalygina</t>
@@ -1964,7 +1985,7 @@
         <v>85</v>
       </c>
       <c r="H17" t="n">
-        <v>0.622459331201855</v>
+        <v>1</v>
       </c>
       <c r="I17" t="s">
         <v>86</v>
@@ -1975,112 +1996,112 @@
         <v>87</v>
       </c>
       <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
         <v>88</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
         <v>89</v>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
         <v>90</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
         <v>93</v>
       </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="F19" t="n">
+        <v>0.232048869591992</v>
+      </c>
+      <c r="G19" t="s">
         <v>94</v>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
         <v>95</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
         <v>97</v>
       </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
         <v>98</v>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
         <v>99</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.232048869591992</v>
-      </c>
-      <c r="G20" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
         <v>102</v>
       </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
         <v>103</v>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.622459331201855</v>
       </c>
       <c r="G21" t="s">
         <v>104</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0.622459331201855</v>
       </c>
       <c r="I21" t="s">
         <v>105</v>
@@ -2613,7 +2634,7 @@
         <v>180</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
@@ -2787,7 +2808,7 @@
         <v>203</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
         <v>204</v>
@@ -3106,7 +3127,7 @@
         <v>251</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
@@ -3164,68 +3185,68 @@
         <v>259</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="G59" t="s">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B60" t="s">
-        <v>262</v>
+        <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>263</v>
+        <v>18</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>18</v>
+        <v>266</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>264</v>
+        <v>18</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B61" t="s">
         <v>151</v>
       </c>
       <c r="C61" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
@@ -3237,24 +3258,24 @@
         <v>0.406145296366207</v>
       </c>
       <c r="G61" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B62" t="s">
         <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
@@ -3272,15 +3293,15 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C63" t="s">
         <v>18</v>
@@ -3289,117 +3310,117 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B64" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C64" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>279</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H64" t="n">
         <v>0.921587657155495</v>
       </c>
       <c r="I64" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B65" t="s">
         <v>22</v>
       </c>
       <c r="C65" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F65" t="n">
         <v>0.203941216842155</v>
       </c>
       <c r="G65" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H65" t="n">
         <v>0.203941216842155</v>
       </c>
       <c r="I65" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B66" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C66" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H66" t="n">
         <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s">
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
@@ -3411,18 +3432,18 @@
         <v>0.159641414055898</v>
       </c>
       <c r="G67" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H67" t="n">
         <v>0.263204195038606</v>
       </c>
       <c r="I67" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B68" t="s">
         <v>16</v>
@@ -3440,18 +3461,18 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
       </c>
       <c r="I68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B69" t="s">
         <v>16</v>
@@ -3469,18 +3490,18 @@
         <v>0</v>
       </c>
       <c r="G69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B70" t="s">
         <v>16</v>
@@ -3498,24 +3519,24 @@
         <v>0</v>
       </c>
       <c r="G70" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B71" t="s">
         <v>244</v>
       </c>
       <c r="C71" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
@@ -3527,18 +3548,18 @@
         <v>0.558971169677543</v>
       </c>
       <c r="G71" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H71" t="n">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B72" t="s">
         <v>10</v>
@@ -3550,24 +3571,24 @@
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F72" t="n">
         <v>0.433950354897655</v>
       </c>
       <c r="G72" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H72" t="n">
         <v>0.433950354897655</v>
       </c>
       <c r="I72" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B73" t="s">
         <v>16</v>
@@ -3579,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F73" t="n">
         <v>1</v>
@@ -3591,70 +3612,70 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B74" t="s">
         <v>138</v>
       </c>
       <c r="C74" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D74" t="n">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F74" t="n">
         <v>0.0451380997519803</v>
       </c>
       <c r="G74" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H74" t="n">
         <v>0.0451380997519803</v>
       </c>
       <c r="I74" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B75" t="s">
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F75" t="n">
         <v>0.263204195038606</v>
       </c>
       <c r="G75" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H75" t="n">
         <v>0.159641414055898</v>
       </c>
       <c r="I75" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B76" t="s">
         <v>16</v>
@@ -3666,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
@@ -3678,18 +3699,18 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B77" t="s">
         <v>32</v>
       </c>
       <c r="C77" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -3707,12 +3728,12 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B78" t="s">
         <v>138</v>
@@ -3724,59 +3745,59 @@
         <v>0</v>
       </c>
       <c r="E78" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F78" t="n">
         <v>0.277184851907928</v>
       </c>
       <c r="G78" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H78" t="n">
         <v>0.277184851907928</v>
       </c>
       <c r="I78" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B79" t="s">
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F79" t="n">
         <v>0.715463180547633</v>
       </c>
       <c r="G79" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H79" t="n">
         <v>0.0968274121847817</v>
       </c>
       <c r="I79" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B80" t="s">
         <v>32</v>
       </c>
       <c r="C80" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
@@ -3794,62 +3815,62 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B81" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="C81" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>337</v>
+        <v>18</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0744201451800741</v>
+        <v>0</v>
       </c>
       <c r="G81" t="s">
+        <v>18</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="s">
         <v>338</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.0744201451800741</v>
-      </c>
-      <c r="I81" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>339</v>
+      </c>
+      <c r="B82" t="s">
+        <v>138</v>
+      </c>
+      <c r="C82" t="s">
         <v>340</v>
       </c>
-      <c r="B82" t="s">
-        <v>88</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="s">
         <v>341</v>
       </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" t="s">
-        <v>18</v>
-      </c>
       <c r="F82" t="n">
-        <v>0.382583907138237</v>
+        <v>0.0744201451800741</v>
       </c>
       <c r="G82" t="s">
         <v>342</v>
       </c>
       <c r="H82" t="n">
-        <v>0.382583907138237</v>
+        <v>0.0744201451800741</v>
       </c>
       <c r="I82" t="s">
         <v>343</v>
@@ -3860,11 +3881,11 @@
         <v>344</v>
       </c>
       <c r="B83" t="s">
+        <v>82</v>
+      </c>
+      <c r="C83" t="s">
         <v>345</v>
       </c>
-      <c r="C83" t="s">
-        <v>18</v>
-      </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
@@ -3872,24 +3893,24 @@
         <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="G83" t="s">
         <v>346</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="I83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B84" t="s">
-        <v>262</v>
+        <v>349</v>
       </c>
       <c r="C84" t="s">
         <v>18</v>
@@ -3901,52 +3922,54 @@
         <v>18</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H84" t="n">
-        <v>0.558971169677543</v>
+        <v>1</v>
       </c>
       <c r="I84" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="C85" t="s">
-        <v>231</v>
+        <v>18</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>18</v>
+        <v>352</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="G85" t="s">
-        <v>18</v>
+        <v>353</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="I85" t="s">
-        <v>231</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>350</v>
-      </c>
-      <c r="B86"/>
+        <v>355</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
       <c r="C86" t="s">
         <v>231</v>
       </c>
@@ -3971,7 +3994,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B87"/>
       <c r="C87" t="s">
@@ -3998,7 +4021,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B88"/>
       <c r="C88" t="s">
@@ -4025,11 +4048,9 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>353</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="B89"/>
       <c r="C89" t="s">
         <v>231</v>
       </c>
@@ -4054,68 +4075,68 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B90" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="C90" t="s">
-        <v>18</v>
+        <v>231</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>355</v>
+        <v>18</v>
       </c>
       <c r="F90" t="n">
-        <v>0.168121111090064</v>
+        <v>0</v>
       </c>
       <c r="G90" t="s">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="H90" t="n">
-        <v>0.168121111090064</v>
+        <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>357</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B91" t="s">
-        <v>244</v>
+        <v>138</v>
       </c>
       <c r="C91" t="s">
         <v>18</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>0.168121111090064</v>
       </c>
       <c r="G91" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H91" t="n">
-        <v>0.558971169677543</v>
+        <v>0.168121111090064</v>
       </c>
       <c r="I91" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B92" t="s">
-        <v>363</v>
+        <v>244</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
@@ -4124,27 +4145,27 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>18</v>
+        <v>365</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="I92" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B93" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C93" t="s">
         <v>18</v>
@@ -4159,21 +4180,21 @@
         <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H93" t="n">
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="C94" t="s">
         <v>18</v>
@@ -4185,53 +4206,53 @@
         <v>18</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="H94" t="n">
-        <v>0.377540668798145</v>
+        <v>1</v>
       </c>
       <c r="I94" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B95" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="C95" t="s">
         <v>18</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F95" t="n">
-        <v>0.101970608421077</v>
+        <v>0.377540668798145</v>
       </c>
       <c r="G95" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H95" t="n">
-        <v>0.101970608421077</v>
+        <v>0.377540668798145</v>
       </c>
       <c r="I95" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B96" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c r="C96" t="s">
         <v>18</v>
@@ -4240,56 +4261,56 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0.101970608421077</v>
       </c>
       <c r="G96" t="s">
-        <v>18</v>
+        <v>380</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>0.101970608421077</v>
       </c>
       <c r="I96" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B97" t="s">
-        <v>366</v>
+        <v>16</v>
       </c>
       <c r="C97" t="s">
         <v>18</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>18</v>
+        <v>279</v>
       </c>
       <c r="F97" t="n">
-        <v>0.406145296366207</v>
+        <v>1</v>
       </c>
       <c r="G97" t="s">
         <v>18</v>
       </c>
       <c r="H97" t="n">
-        <v>0.669620389113773</v>
+        <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>18</v>
+        <v>279</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B98" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C98" t="s">
         <v>18</v>
@@ -4301,13 +4322,13 @@
         <v>18</v>
       </c>
       <c r="F98" t="n">
+        <v>0.406145296366207</v>
+      </c>
+      <c r="G98" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" t="n">
         <v>0.669620389113773</v>
-      </c>
-      <c r="G98" t="s">
-        <v>18</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0.406145296366207</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
@@ -4315,10 +4336,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B99" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C99" t="s">
         <v>18</v>
@@ -4330,15 +4351,44 @@
         <v>18</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G99" t="s">
         <v>18</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="I99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>385</v>
+      </c>
+      <c r="B100" t="s">
+        <v>372</v>
+      </c>
+      <c r="C100" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="s">
+        <v>18</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" t="s">
         <v>18</v>
       </c>
     </row>
